--- a/Anthem Visit Plans.xlsx
+++ b/Anthem Visit Plans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kweons01\Desktop\Strategic Initiatives - So Youn\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kweons01\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5218B5DA-8FFE-410D-85EA-195D5405BBD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F380A624-E649-4A1C-BAB1-D50C9380621E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{61B8E5EA-6E2E-47C7-A991-C2216562D2C1}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$64</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="69">
   <si>
     <t>BENEFIT_PLAN_ID</t>
   </si>
@@ -246,12 +246,6 @@
   </si>
   <si>
     <t>EMPIRE BC/BS CHP B</t>
-  </si>
-  <si>
-    <t>CIGNA OPEN ACCESS PLUS</t>
-  </si>
-  <si>
-    <t>ConEd Cigna-to-Anthem</t>
   </si>
 </sst>
 </file>
@@ -650,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD645ABD-EC8C-47A5-9471-48EB1E079B09}">
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -1002,43 +996,43 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>8001005019</v>
+        <v>8001004019</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>8001004019</v>
+        <v>8003004006</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>8003004006</v>
+        <v>8001004028</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>8001004028</v>
+        <v>8001004004</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
@@ -1046,10 +1040,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>8001004004</v>
+        <v>8001004020</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>4</v>
@@ -1057,10 +1051,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>8001004020</v>
+        <v>8001004037</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -1068,10 +1062,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>8001004037</v>
+        <v>8009002016</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
@@ -1079,21 +1073,21 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>8009002016</v>
+        <v>8003004003</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>8003004003</v>
+        <v>8003004007</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>28</v>
@@ -1101,21 +1095,21 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>8003004007</v>
+        <v>8001004029</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>8001004029</v>
+        <v>8001004030</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>11</v>
@@ -1123,7 +1117,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>8001004030</v>
+        <v>8008010009</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>10</v>
@@ -1134,43 +1128,43 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>8008010009</v>
+        <v>8003004004</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>8003004004</v>
+        <v>8005010003</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>8005010003</v>
+        <v>8001004005</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>8001004005</v>
+        <v>8001004006</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -1178,10 +1172,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>8001004006</v>
+        <v>8001004046</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -1189,10 +1183,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>8001004046</v>
+        <v>8001004038</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -1200,21 +1194,21 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>8001004038</v>
+        <v>8005010001</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>8005010001</v>
+        <v>8005010005</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>30</v>
@@ -1222,21 +1216,21 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>8005010005</v>
+        <v>8001173002</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>8001173002</v>
+        <v>8001004027</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -1244,10 +1238,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>8001004027</v>
+        <v>8001004047</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
@@ -1255,10 +1249,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>8001004047</v>
+        <v>8001004010</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
@@ -1266,10 +1260,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>8001004010</v>
+        <v>8001004011</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>4</v>
@@ -1277,10 +1271,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>8001004011</v>
+        <v>8001004044</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>4</v>
@@ -1288,10 +1282,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>8001004044</v>
+        <v>8001173005</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>4</v>
@@ -1299,10 +1293,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>8001173005</v>
+        <v>8001004040</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>4</v>
@@ -1310,10 +1304,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>8001004040</v>
+        <v>8001004041</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>4</v>
@@ -1321,65 +1315,50 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>8001004041</v>
+        <v>8001004026</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>8001004026</v>
+        <v>8001004021</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>8001004021</v>
+        <v>8001004024</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>8001004024</v>
+        <v>8001160601</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
-        <v>8001160601</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C65" s="1" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1" xr:uid="{BD645ABD-EC8C-47A5-9471-48EB1E079B09}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C65">
-      <sortCondition ref="B1"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:C64" xr:uid="{BD645ABD-EC8C-47A5-9471-48EB1E079B09}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Anthem Visit Plans.xlsx
+++ b/Anthem Visit Plans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kweons01\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F380A624-E649-4A1C-BAB1-D50C9380621E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE16EAD-A6A9-417B-BFF5-4E69C7A00555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{61B8E5EA-6E2E-47C7-A991-C2216562D2C1}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{61B8E5EA-6E2E-47C7-A991-C2216562D2C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="70">
   <si>
     <t>BENEFIT_PLAN_ID</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>EMPIRE BC/BS CHP B</t>
+  </si>
+  <si>
+    <t>ANTHEM BC/BS EXCHANGE INDIVIDUAL NETWORK</t>
   </si>
 </sst>
 </file>
@@ -644,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD645ABD-EC8C-47A5-9471-48EB1E079B09}">
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -1354,7 +1357,47 @@
         <v>8</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>56</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>43</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>48</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
